--- a/DataTables/Datas/#Entity.xlsx
+++ b/DataTables/Datas/#Entity.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="8.21428571428571" customWidth="1" style="3" min="1" max="1"/>
@@ -1366,32 +1366,62 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
+      <c r="B21" s="0" t="n">
         <v>300001</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>Gem_300001</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>经验宝石</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
+      <c r="B22" s="0" t="n">
         <v>500002</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>DamageText_500002</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>伤害飘字</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>201002</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Enemy_201002</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>快速怪</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>201003</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Enemy_201003</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>坦克怪</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/#Entity.xlsx
+++ b/DataTables/Datas/#Entity.xlsx
@@ -649,13 +649,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1041,61 +1041,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="8.21428571428571" customWidth="1" style="3" min="1" max="1"/>
-    <col width="11.1607142857143" customWidth="1" style="3" min="2" max="2"/>
-    <col width="23.8035714285714" customWidth="1" style="3" min="3" max="3"/>
-    <col width="21.7232142857143" customWidth="1" style="3" min="4" max="4"/>
+    <col width="8.21428571428571" customWidth="1" style="1" min="1" max="1"/>
+    <col width="11.1607142857143" customWidth="1" style="1" min="2" max="2"/>
+    <col width="23.8035714285714" customWidth="1" style="1" min="3" max="3"/>
+    <col width="21.7232142857143" customWidth="1" style="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -1124,196 +1124,196 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>PlayerShip</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>玩家战机</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
+      <c r="E5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>10001</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>EnemyShip</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>敌人战机</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
+      <c r="E6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>PlayerBolt</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>玩家子弹</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
+      <c r="E7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>50001</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>EnemyBolt</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>敌人子弹</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
+      <c r="E8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>60000</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Asteroid01</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>小行星01</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
+      <c r="E9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>60001</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Asteroid02</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>小行星02</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
+      <c r="E10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="3" t="n">
         <v>60002</v>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Asteroid03</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>小行星03</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
+      <c r="E11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>70000</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>PlayerExplosion</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>玩家死亡特效</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
+      <c r="E12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="3" t="n">
         <v>70001</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>EnemyExplosion</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>敌人死亡特效</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
+      <c r="E13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="3" t="n">
         <v>70002</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>AsteroidExplosion</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>小行星死亡特效</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
+      <c r="E14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <v>70003</v>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>PlayerEngine</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>玩家推进器</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
+      <c r="E15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>70004</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>EnemyEngine</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>敌人推进器</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
+      <c r="E16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="0" t="n">
@@ -1352,76 +1352,136 @@
     </row>
     <row r="20">
       <c r="B20" s="0" t="n">
-        <v>701001</v>
+        <v>500003</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>Effect_701001</t>
+          <t>Orbit_500003</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>弹幕命中特效</t>
+          <t>环绕</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="n">
-        <v>300001</v>
+        <v>701001</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>Gem_300001</t>
+          <t>Effect_701001</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>经验宝石</t>
+          <t>弹幕命中特效</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>Gem_300001</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>经验宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="n">
         <v>500002</v>
       </c>
-      <c r="C22" s="0" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>DamageText_500002</t>
         </is>
       </c>
-      <c r="D22" s="0" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>伤害飘字</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" t="n">
+    <row r="24">
+      <c r="B24" s="0" t="n">
         <v>201002</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>Enemy_201002</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>快速怪</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="n">
+    <row r="25">
+      <c r="B25" s="0" t="n">
         <v>201003</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>Enemy_201003</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>坦克怪</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="n">
+        <v>201004</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>Enemy_201004</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>群聚怪</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="0" t="n">
+        <v>201005</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>Enemy_201005</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>蝙蝠</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>300002</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chest_300002</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>宝箱</t>
         </is>
       </c>
     </row>
